--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_h_8.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02682939948240399</v>
+        <v>0.02188976703741924</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008437736353898044</v>
+        <v>0.008432213998538026</v>
       </c>
       <c r="C2" t="n">
-        <v>50904648</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50904648</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>35053089</v>
+        <v>4103873</v>
       </c>
       <c r="L2" t="n">
-        <v>18744159</v>
+        <v>1963715</v>
       </c>
       <c r="M2" t="n">
-        <v>4387875</v>
+        <v>383012</v>
       </c>
       <c r="N2" t="n">
-        <v>208789</v>
+        <v>14811</v>
       </c>
       <c r="O2" t="n">
-        <v>2627620</v>
+        <v>219799</v>
       </c>
       <c r="P2" t="n">
-        <v>1073570</v>
+        <v>93223</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999901652336121</v>
+        <v>0.9999962449073792</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8457244038581848</v>
+        <v>0.7769218683242798</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7092496156692505</v>
+        <v>0.5956236124038696</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6367554664611816</v>
+        <v>0.5020797252655029</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2475334256887436</v>
+        <v>0.07789278030395508</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6946702003479004</v>
+        <v>0.5489910840988159</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7802833318710327</v>
+        <v>0.679948627948761</v>
       </c>
       <c r="X2" t="n">
-        <v>50904648</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50904648</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>38791394</v>
+        <v>4813274</v>
       </c>
       <c r="AG2" t="n">
-        <v>24034613</v>
+        <v>3010697</v>
       </c>
       <c r="AH2" t="n">
-        <v>6424509</v>
+        <v>804213</v>
       </c>
       <c r="AI2" t="n">
-        <v>473880</v>
+        <v>59267</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3678844</v>
+        <v>460431</v>
       </c>
       <c r="AK2" t="n">
-        <v>1441067</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9561742544174194</v>
+        <v>0.9555724859237671</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114837646484375</v>
+        <v>0.9118132591247559</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8578961491584778</v>
+        <v>0.8582125902175903</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6616310477256775</v>
+        <v>0.6612037420272827</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019256830215454</v>
+        <v>0.9019888043403625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314501285552979</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.006810924910237644</v>
+        <v>0.005424360942438176</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002021420070486094</v>
+        <v>0.002020802637879015</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>35053089</v>
+        <v>4103873</v>
       </c>
       <c r="E3" t="n">
-        <v>5273709</v>
+        <v>888264</v>
       </c>
       <c r="F3" t="n">
-        <v>154637</v>
+        <v>29113</v>
       </c>
       <c r="G3" t="n">
-        <v>20094</v>
+        <v>3797</v>
       </c>
       <c r="H3" t="n">
-        <v>9618</v>
+        <v>1849</v>
       </c>
       <c r="I3" t="n">
-        <v>736</v>
+        <v>136</v>
       </c>
       <c r="J3" t="n">
-        <v>80768451</v>
+        <v>10069596</v>
       </c>
       <c r="K3" t="n">
-        <v>84767364</v>
+        <v>10210613</v>
       </c>
       <c r="L3" t="n">
-        <v>97574034</v>
+        <v>11773302</v>
       </c>
       <c r="M3" t="n">
-        <v>121674715</v>
+        <v>15097384</v>
       </c>
       <c r="N3" t="n">
-        <v>130322009</v>
+        <v>16150891</v>
       </c>
       <c r="O3" t="n">
-        <v>126437424</v>
+        <v>15724497</v>
       </c>
       <c r="P3" t="n">
-        <v>129823753</v>
+        <v>16178530</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8652539253234863</v>
+        <v>0.8163598775863647</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7095875144004822</v>
+        <v>0.5933557748794556</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5853800773620605</v>
+        <v>0.4079903960227966</v>
       </c>
       <c r="U3" t="n">
-        <v>0.291237860918045</v>
+        <v>0.164980947971344</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6438267827033997</v>
+        <v>0.4301914274692535</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6937245726585388</v>
+        <v>0.4815486371517181</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38791394</v>
+        <v>4813274</v>
       </c>
       <c r="Z3" t="n">
-        <v>1596247</v>
+        <v>198388</v>
       </c>
       <c r="AA3" t="n">
-        <v>68802</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>54902</v>
+        <v>6867</v>
       </c>
       <c r="AC3" t="n">
-        <v>326</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80768952</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>89383707</v>
+        <v>11165177</v>
       </c>
       <c r="AG3" t="n">
-        <v>102923975</v>
+        <v>12815311</v>
       </c>
       <c r="AH3" t="n">
-        <v>123113659</v>
+        <v>15344357</v>
       </c>
       <c r="AI3" t="n">
-        <v>130714348</v>
+        <v>16295858</v>
       </c>
       <c r="AJ3" t="n">
-        <v>127192314</v>
+        <v>15855036</v>
       </c>
       <c r="AK3" t="n">
-        <v>130020000</v>
+        <v>16209148</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575306177139282</v>
+        <v>0.9574769735336304</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098653793334961</v>
+        <v>0.9097115993499756</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570844531059265</v>
+        <v>0.8566603064537048</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610108613967896</v>
+        <v>0.6601800322532654</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901400625705719</v>
+        <v>0.9011573195457458</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311955571174622</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06360872249125075</v>
+        <v>0.05380564674132016</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03192520221778363</v>
+        <v>0.03191057304788653</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5976174</v>
+        <v>1090210</v>
       </c>
       <c r="E4" t="n">
-        <v>18744159</v>
+        <v>1963715</v>
       </c>
       <c r="F4" t="n">
-        <v>1436216</v>
+        <v>201603</v>
       </c>
       <c r="G4" t="n">
-        <v>96515</v>
+        <v>25825</v>
       </c>
       <c r="H4" t="n">
-        <v>145822</v>
+        <v>25030</v>
       </c>
       <c r="I4" t="n">
-        <v>16669</v>
+        <v>3123</v>
       </c>
       <c r="J4" t="n">
-        <v>501</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>6394325</v>
+        <v>1178348</v>
       </c>
       <c r="L4" t="n">
-        <v>7683996</v>
+        <v>1333191</v>
       </c>
       <c r="M4" t="n">
-        <v>2503114</v>
+        <v>379839</v>
       </c>
       <c r="N4" t="n">
-        <v>634689</v>
+        <v>175335</v>
       </c>
       <c r="O4" t="n">
-        <v>1154923</v>
+        <v>180570</v>
       </c>
       <c r="P4" t="n">
-        <v>302302</v>
+        <v>43880</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999950528144836</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.855377733707428</v>
+        <v>0.7961527705192566</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7094185352325439</v>
+        <v>0.5944875478744507</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6099879145622253</v>
+        <v>0.4501712322235107</v>
       </c>
       <c r="U4" t="n">
-        <v>0.267613023519516</v>
+        <v>0.1058230921626091</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6682828664779663</v>
+        <v>0.4823845624923706</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7344624996185303</v>
+        <v>0.5638039112091064</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1660174</v>
+        <v>208961</v>
       </c>
       <c r="Z4" t="n">
-        <v>24034613</v>
+        <v>3010697</v>
       </c>
       <c r="AA4" t="n">
-        <v>666659</v>
+        <v>83070</v>
       </c>
       <c r="AB4" t="n">
-        <v>44412</v>
+        <v>5580</v>
       </c>
       <c r="AC4" t="n">
-        <v>9168</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1777982</v>
+        <v>223784</v>
       </c>
       <c r="AG4" t="n">
-        <v>2334055</v>
+        <v>291182</v>
       </c>
       <c r="AH4" t="n">
-        <v>1064170</v>
+        <v>132866</v>
       </c>
       <c r="AI4" t="n">
-        <v>242350</v>
+        <v>30368</v>
       </c>
       <c r="AJ4" t="n">
-        <v>400033</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106055</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568519592285156</v>
+        <v>0.9565237760543823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106738567352295</v>
+        <v>0.9107611775398254</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8574901223182678</v>
+        <v>0.8574357628822327</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613208055496216</v>
+        <v>0.660691499710083</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901663064956665</v>
+        <v>0.9015728235244751</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313228130340576</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>291652</v>
+        <v>64758</v>
       </c>
       <c r="E5" t="n">
-        <v>1996792</v>
+        <v>356470</v>
       </c>
       <c r="F5" t="n">
-        <v>4387875</v>
+        <v>383012</v>
       </c>
       <c r="G5" t="n">
-        <v>215283</v>
+        <v>52761</v>
       </c>
       <c r="H5" t="n">
-        <v>543723</v>
+        <v>71064</v>
       </c>
       <c r="I5" t="n">
-        <v>60401</v>
+        <v>10711</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5458822</v>
+        <v>923166</v>
       </c>
       <c r="L5" t="n">
-        <v>7671411</v>
+        <v>1345792</v>
       </c>
       <c r="M5" t="n">
-        <v>3107896</v>
+        <v>555765</v>
       </c>
       <c r="N5" t="n">
-        <v>508113</v>
+        <v>74963</v>
       </c>
       <c r="O5" t="n">
-        <v>1453633</v>
+        <v>291134</v>
       </c>
       <c r="P5" t="n">
-        <v>473975</v>
+        <v>100367</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999961853027344</v>
+        <v>0.9999985098838806</v>
       </c>
       <c r="R5" t="n">
-        <v>0.909980833530426</v>
+        <v>0.8719837665557861</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8833827972412109</v>
+        <v>0.83680659532547</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9573869705200195</v>
+        <v>0.9430065751075745</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9913209676742554</v>
+        <v>0.9847527742385864</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9801892042160034</v>
+        <v>0.9712656140327454</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9941045641899109</v>
+        <v>0.9912130236625671</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>65006</v>
+        <v>8176</v>
       </c>
       <c r="Z5" t="n">
-        <v>687519</v>
+        <v>86508</v>
       </c>
       <c r="AA5" t="n">
-        <v>6424509</v>
+        <v>804213</v>
       </c>
       <c r="AB5" t="n">
-        <v>79964</v>
+        <v>10008</v>
       </c>
       <c r="AC5" t="n">
-        <v>233709</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1720517</v>
+        <v>213765</v>
       </c>
       <c r="AG5" t="n">
-        <v>2380957</v>
+        <v>298810</v>
       </c>
       <c r="AH5" t="n">
-        <v>1071262</v>
+        <v>134564</v>
       </c>
       <c r="AI5" t="n">
-        <v>243022</v>
+        <v>30507</v>
       </c>
       <c r="AJ5" t="n">
-        <v>402409</v>
+        <v>50502</v>
       </c>
       <c r="AK5" t="n">
-        <v>106478</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734305143356323</v>
+        <v>0.9733461737632751</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641916751861572</v>
+        <v>0.9640599489212036</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837824106216431</v>
+        <v>0.9837091565132141</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963138103485107</v>
+        <v>0.9962917566299438</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939058423042297</v>
+        <v>0.9938759207725525</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983859062194824</v>
+        <v>0.9983792304992676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>107356</v>
+        <v>17730</v>
       </c>
       <c r="E6" t="n">
-        <v>148581</v>
+        <v>23875</v>
       </c>
       <c r="F6" t="n">
-        <v>164537</v>
+        <v>23896</v>
       </c>
       <c r="G6" t="n">
-        <v>208789</v>
+        <v>14811</v>
       </c>
       <c r="H6" t="n">
-        <v>77643</v>
+        <v>8140</v>
       </c>
       <c r="I6" t="n">
-        <v>9908</v>
+        <v>1316</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>52354</v>
+        <v>6591</v>
       </c>
       <c r="Z6" t="n">
-        <v>43154</v>
+        <v>5395</v>
       </c>
       <c r="AA6" t="n">
-        <v>87663</v>
+        <v>11026</v>
       </c>
       <c r="AB6" t="n">
-        <v>473880</v>
+        <v>59267</v>
       </c>
       <c r="AC6" t="n">
-        <v>56003</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>146</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>18606</v>
+        <v>5529</v>
       </c>
       <c r="E7" t="n">
-        <v>244098</v>
+        <v>58960</v>
       </c>
       <c r="F7" t="n">
-        <v>701542</v>
+        <v>114960</v>
       </c>
       <c r="G7" t="n">
-        <v>274653</v>
+        <v>83086</v>
       </c>
       <c r="H7" t="n">
-        <v>2627620</v>
+        <v>219799</v>
       </c>
       <c r="I7" t="n">
-        <v>214588</v>
+        <v>28594</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>6487</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>238395</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60944</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3678844</v>
+        <v>460431</v>
       </c>
       <c r="AD7" t="n">
-        <v>96359</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>537</v>
+        <v>121</v>
       </c>
       <c r="E8" t="n">
-        <v>20816</v>
+        <v>5622</v>
       </c>
       <c r="F8" t="n">
-        <v>46182</v>
+        <v>10267</v>
       </c>
       <c r="G8" t="n">
-        <v>28144</v>
+        <v>9866</v>
       </c>
       <c r="H8" t="n">
-        <v>378117</v>
+        <v>74487</v>
       </c>
       <c r="I8" t="n">
-        <v>1073570</v>
+        <v>93223</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2651</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2128</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100827</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1441067</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
